--- a/virtual-physics-lab/app/dl/TJC_Q1_double_pendulum.xlsx
+++ b/virtual-physics-lab/app/dl/TJC_Q1_double_pendulum.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -91,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,9 +101,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -680,92 +684,92 @@
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="B6" s="6" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>10.1</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>10.48</v>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
+      <c r="B7" s="6" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
+      <c r="B8" s="6" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>20.1</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
+      <c r="B9" s="6" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>24.9</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
+      <c r="B10" s="6" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>30.2</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="B11" s="6" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>35.3</v>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
+      <c r="B12" s="6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -851,30 +855,30 @@
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="D6" s="7">
-        <f>(B6+C6)/20</f>
-        <v/>
-      </c>
-      <c r="E6" s="7">
+      <c r="B6" s="6" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D6" s="8">
+        <f>ROUND((B6+C6)/20,3)</f>
+        <v/>
+      </c>
+      <c r="E6" s="8">
         <f>D6^4</f>
         <v/>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <f>SLOPE(E6:E12,A6:A12)</f>
         <v/>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>s⁴ cm⁻¹</t>
         </is>
@@ -884,30 +888,30 @@
       <c r="A7" s="5" t="n">
         <v>10.1</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>10.48</v>
-      </c>
-      <c r="D7" s="7">
-        <f>(B7+C7)/20</f>
-        <v/>
-      </c>
-      <c r="E7" s="7">
+      <c r="B7" s="6" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="D7" s="8">
+        <f>ROUND((B7+C7)/20,3)</f>
+        <v/>
+      </c>
+      <c r="E7" s="8">
         <f>D7^4</f>
         <v/>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="8">
         <f>INTERCEPT(E6:E12,A6:A12)</f>
         <v/>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>s⁴</t>
         </is>
@@ -917,17 +921,17 @@
       <c r="A8" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="D8" s="7">
-        <f>(B8+C8)/20</f>
-        <v/>
-      </c>
-      <c r="E8" s="7">
+      <c r="B8" s="6" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="D8" s="8">
+        <f>ROUND((B8+C8)/20,3)</f>
+        <v/>
+      </c>
+      <c r="E8" s="8">
         <f>D8^4</f>
         <v/>
       </c>
@@ -936,17 +940,17 @@
       <c r="A9" s="5" t="n">
         <v>20.1</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="D9" s="7">
-        <f>(B9+C9)/20</f>
-        <v/>
-      </c>
-      <c r="E9" s="7">
+      <c r="B9" s="6" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="D9" s="8">
+        <f>ROUND((B9+C9)/20,3)</f>
+        <v/>
+      </c>
+      <c r="E9" s="8">
         <f>D9^4</f>
         <v/>
       </c>
@@ -955,17 +959,17 @@
       <c r="A10" s="5" t="n">
         <v>24.9</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="D10" s="7">
-        <f>(B10+C10)/20</f>
-        <v/>
-      </c>
-      <c r="E10" s="7">
+      <c r="B10" s="6" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="D10" s="8">
+        <f>ROUND((B10+C10)/20,3)</f>
+        <v/>
+      </c>
+      <c r="E10" s="8">
         <f>D10^4</f>
         <v/>
       </c>
@@ -974,17 +978,17 @@
       <c r="A11" s="5" t="n">
         <v>30.2</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="D11" s="7">
-        <f>(B11+C11)/20</f>
-        <v/>
-      </c>
-      <c r="E11" s="7">
+      <c r="B11" s="6" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="D11" s="8">
+        <f>ROUND((B11+C11)/20,3)</f>
+        <v/>
+      </c>
+      <c r="E11" s="8">
         <f>D11^4</f>
         <v/>
       </c>
@@ -993,17 +997,17 @@
       <c r="A12" s="5" t="n">
         <v>35.3</v>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="D12" s="7">
-        <f>(B12+C12)/20</f>
-        <v/>
-      </c>
-      <c r="E12" s="7">
+      <c r="B12" s="6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="D12" s="8">
+        <f>ROUND((B12+C12)/20,3)</f>
+        <v/>
+      </c>
+      <c r="E12" s="8">
         <f>D12^4</f>
         <v/>
       </c>
